--- a/VerveStacks_SAU_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A49274EC-1AC1-4F48-8430-BC24448C2EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B9319BA-D7C4-4D65-9666-EDC0506044A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{50B33629-B786-4179-8BF4-E72F7FA1CD07}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0B792C06-9948-4B31-B49E-FC0B3B61D9B3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -685,7 +685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C251DDCB-87CE-44E7-BCF0-5EBE02912C5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE84494-B318-449A-BBD9-2C7B366470DD}">
   <dimension ref="B3:R31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_SAU_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B9319BA-D7C4-4D65-9666-EDC0506044A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{357D3B03-21EF-4C64-910A-1EDB3DD5CF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0B792C06-9948-4B31-B49E-FC0B3B61D9B3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2C01D35C-8632-4079-8D47-585E5002FA99}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="223">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -302,7 +302,7 @@
     <t>grid link -100.0 km- way/207785816-380;way/900157271-380</t>
   </si>
   <si>
-    <t>~grid_nodes_geo</t>
+    <t>~commodity_geo</t>
   </si>
   <si>
     <t>commodity</t>
@@ -311,10 +311,403 @@
     <t>region</t>
   </si>
   <si>
-    <t>lon</t>
+    <t>lng</t>
   </si>
   <si>
     <t>lat</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_001</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_002</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_003</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_004</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_005</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_006</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_007</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_008</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_009</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_010</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_011</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_012</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_013</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_014</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_015</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_016</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_017</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_018</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_019</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_020</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_021</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_022</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_023</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_024</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_025</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_026</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_027</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_028</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_029</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_030</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_031</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_032</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_033</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_034</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_035</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_036</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_037</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_038</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_039</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_040</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_041</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_042</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_043</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_044</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_045</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_046</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_047</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_048</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_049</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_050</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_051</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_052</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_053</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_054</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_055</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_056</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_057</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_058</t>
+  </si>
+  <si>
+    <t>elc_spv_SAU_059</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_001</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_002</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_003</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_004</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_005</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_006</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_007</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_008</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_009</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_010</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_011</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_012</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_013</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_014</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_015</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_001</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_002</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_003</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_004</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_005</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_006</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_007</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_008</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_009</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_010</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_011</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_012</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_013</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_014</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_015</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_016</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_017</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_018</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_019</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_020</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_021</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_022</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_023</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_024</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_025</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_026</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_027</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_028</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_029</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_030</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_031</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_032</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_033</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_034</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_035</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_036</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_037</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_038</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_039</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_040</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_041</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_042</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_043</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_044</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_045</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_046</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_047</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_048</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_049</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_050</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_051</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_052</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_053</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_054</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_055</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_056</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_057</t>
   </si>
 </sst>
 </file>
@@ -685,8 +1078,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE84494-B318-449A-BBD9-2C7B366470DD}">
-  <dimension ref="B3:R31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9308648-2322-4D5E-A921-954EF84482A9}">
+  <dimension ref="B3:R154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
@@ -1548,6 +1941,18 @@
       <c r="L24" t="s">
         <v>79</v>
       </c>
+      <c r="O24" t="s">
+        <v>92</v>
+      </c>
+      <c r="P24" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24">
+        <v>39.39312488889076</v>
+      </c>
+      <c r="R24">
+        <v>22.2315833150877</v>
+      </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
@@ -1577,6 +1982,18 @@
       <c r="L25" t="s">
         <v>80</v>
       </c>
+      <c r="O25" t="s">
+        <v>93</v>
+      </c>
+      <c r="P25" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25">
+        <v>40.520899135365134</v>
+      </c>
+      <c r="R25">
+        <v>21.921514906431515</v>
+      </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
@@ -1606,6 +2023,18 @@
       <c r="L26" t="s">
         <v>81</v>
       </c>
+      <c r="O26" t="s">
+        <v>94</v>
+      </c>
+      <c r="P26" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26">
+        <v>40.727726187894881</v>
+      </c>
+      <c r="R26">
+        <v>20.089002138663773</v>
+      </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
@@ -1635,6 +2064,18 @@
       <c r="L27" t="s">
         <v>82</v>
       </c>
+      <c r="O27" t="s">
+        <v>95</v>
+      </c>
+      <c r="P27" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27">
+        <v>37.550862354821653</v>
+      </c>
+      <c r="R27">
+        <v>25.002638406668677</v>
+      </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
@@ -1664,6 +2105,18 @@
       <c r="L28" t="s">
         <v>83</v>
       </c>
+      <c r="O28" t="s">
+        <v>96</v>
+      </c>
+      <c r="P28" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28">
+        <v>38.929980052052628</v>
+      </c>
+      <c r="R28">
+        <v>25.61761850610316</v>
+      </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
@@ -1693,6 +2146,18 @@
       <c r="L29" t="s">
         <v>84</v>
       </c>
+      <c r="O29" t="s">
+        <v>97</v>
+      </c>
+      <c r="P29" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29">
+        <v>40.391600129609103</v>
+      </c>
+      <c r="R29">
+        <v>23.806012014599041</v>
+      </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
@@ -1722,6 +2187,18 @@
       <c r="L30" t="s">
         <v>85</v>
       </c>
+      <c r="O30" t="s">
+        <v>98</v>
+      </c>
+      <c r="P30" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q30">
+        <v>40.482950196466128</v>
+      </c>
+      <c r="R30">
+        <v>26.154513528878045</v>
+      </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
@@ -1750,6 +2227,1740 @@
       </c>
       <c r="L31" t="s">
         <v>86</v>
+      </c>
+      <c r="O31" t="s">
+        <v>99</v>
+      </c>
+      <c r="P31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q31">
+        <v>38.204468966786592</v>
+      </c>
+      <c r="R31">
+        <v>26.948835241942891</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O32" t="s">
+        <v>100</v>
+      </c>
+      <c r="P32" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32">
+        <v>36.827747931957013</v>
+      </c>
+      <c r="R32">
+        <v>27.439232020157828</v>
+      </c>
+    </row>
+    <row r="33" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O33" t="s">
+        <v>101</v>
+      </c>
+      <c r="P33" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33">
+        <v>36.71763594919657</v>
+      </c>
+      <c r="R33">
+        <v>29.345974506542703</v>
+      </c>
+    </row>
+    <row r="34" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O34" t="s">
+        <v>102</v>
+      </c>
+      <c r="P34" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q34">
+        <v>35.708639585274682</v>
+      </c>
+      <c r="R34">
+        <v>28.69156222298092</v>
+      </c>
+    </row>
+    <row r="35" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O35" t="s">
+        <v>103</v>
+      </c>
+      <c r="P35" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35">
+        <v>39.904978000917424</v>
+      </c>
+      <c r="R35">
+        <v>27.8513691167643</v>
+      </c>
+    </row>
+    <row r="36" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O36" t="s">
+        <v>104</v>
+      </c>
+      <c r="P36" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q36">
+        <v>40.010949804559182</v>
+      </c>
+      <c r="R36">
+        <v>29.535651150689201</v>
+      </c>
+    </row>
+    <row r="37" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O37" t="s">
+        <v>105</v>
+      </c>
+      <c r="P37" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q37">
+        <v>38.16952306246003</v>
+      </c>
+      <c r="R37">
+        <v>28.648444362714251</v>
+      </c>
+    </row>
+    <row r="38" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O38" t="s">
+        <v>106</v>
+      </c>
+      <c r="P38" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q38">
+        <v>40.339871280072401</v>
+      </c>
+      <c r="R38">
+        <v>31.126058329867419</v>
+      </c>
+    </row>
+    <row r="39" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O39" t="s">
+        <v>107</v>
+      </c>
+      <c r="P39" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q39">
+        <v>38.46721871547205</v>
+      </c>
+      <c r="R39">
+        <v>30.320245662730269</v>
+      </c>
+    </row>
+    <row r="40" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O40" t="s">
+        <v>108</v>
+      </c>
+      <c r="P40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q40">
+        <v>38.251302364724125</v>
+      </c>
+      <c r="R40">
+        <v>31.424694512280688</v>
+      </c>
+    </row>
+    <row r="41" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O41" t="s">
+        <v>109</v>
+      </c>
+      <c r="P41" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q41">
+        <v>42.094699264384872</v>
+      </c>
+      <c r="R41">
+        <v>30.606942992969937</v>
+      </c>
+    </row>
+    <row r="42" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O42" t="s">
+        <v>110</v>
+      </c>
+      <c r="P42" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42">
+        <v>41.971169352852478</v>
+      </c>
+      <c r="R42">
+        <v>28.389667588256152</v>
+      </c>
+    </row>
+    <row r="43" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O43" t="s">
+        <v>111</v>
+      </c>
+      <c r="P43" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43">
+        <v>42.400424261290787</v>
+      </c>
+      <c r="R43">
+        <v>29.539330962744486</v>
+      </c>
+    </row>
+    <row r="44" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O44" t="s">
+        <v>112</v>
+      </c>
+      <c r="P44" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44">
+        <v>45.268801511215067</v>
+      </c>
+      <c r="R44">
+        <v>26.715690945611929</v>
+      </c>
+    </row>
+    <row r="45" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O45" t="s">
+        <v>113</v>
+      </c>
+      <c r="P45" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45">
+        <v>44.346565605958965</v>
+      </c>
+      <c r="R45">
+        <v>25.603806388220946</v>
+      </c>
+    </row>
+    <row r="46" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O46" t="s">
+        <v>114</v>
+      </c>
+      <c r="P46" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q46">
+        <v>41.951645063414766</v>
+      </c>
+      <c r="R46">
+        <v>25.864310129376456</v>
+      </c>
+    </row>
+    <row r="47" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P47" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47">
+        <v>42.811868587324682</v>
+      </c>
+      <c r="R47">
+        <v>27.289093260037166</v>
+      </c>
+    </row>
+    <row r="48" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O48" t="s">
+        <v>116</v>
+      </c>
+      <c r="P48" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48">
+        <v>47.014991007425522</v>
+      </c>
+      <c r="R48">
+        <v>26.649329297407171</v>
+      </c>
+    </row>
+    <row r="49" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O49" t="s">
+        <v>117</v>
+      </c>
+      <c r="P49" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49">
+        <v>46.989567717119449</v>
+      </c>
+      <c r="R49">
+        <v>28.396996856250631</v>
+      </c>
+    </row>
+    <row r="50" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O50" t="s">
+        <v>118</v>
+      </c>
+      <c r="P50" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q50">
+        <v>48.121633687319957</v>
+      </c>
+      <c r="R50">
+        <v>27.709791417169715</v>
+      </c>
+    </row>
+    <row r="51" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O51" t="s">
+        <v>119</v>
+      </c>
+      <c r="P51" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q51">
+        <v>44.092150043004438</v>
+      </c>
+      <c r="R51">
+        <v>28.788524158982906</v>
+      </c>
+    </row>
+    <row r="52" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O52" t="s">
+        <v>120</v>
+      </c>
+      <c r="P52" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52">
+        <v>45.51103416905697</v>
+      </c>
+      <c r="R52">
+        <v>28.254207374178581</v>
+      </c>
+    </row>
+    <row r="53" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O53" t="s">
+        <v>121</v>
+      </c>
+      <c r="P53" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q53">
+        <v>47.151188215817719</v>
+      </c>
+      <c r="R53">
+        <v>22.192431018248069</v>
+      </c>
+    </row>
+    <row r="54" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O54" t="s">
+        <v>122</v>
+      </c>
+      <c r="P54" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q54">
+        <v>43.858370632906535</v>
+      </c>
+      <c r="R54">
+        <v>22.237465187627222</v>
+      </c>
+    </row>
+    <row r="55" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O55" t="s">
+        <v>123</v>
+      </c>
+      <c r="P55" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q55">
+        <v>45.529725915580549</v>
+      </c>
+      <c r="R55">
+        <v>22.911842322278609</v>
+      </c>
+    </row>
+    <row r="56" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O56" t="s">
+        <v>124</v>
+      </c>
+      <c r="P56" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q56">
+        <v>46.570418072861251</v>
+      </c>
+      <c r="R56">
+        <v>17.857499815825943</v>
+      </c>
+    </row>
+    <row r="57" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O57" t="s">
+        <v>125</v>
+      </c>
+      <c r="P57" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57">
+        <v>47.195323985961991</v>
+      </c>
+      <c r="R57">
+        <v>19.883586940739757</v>
+      </c>
+    </row>
+    <row r="58" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O58" t="s">
+        <v>126</v>
+      </c>
+      <c r="P58" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58">
+        <v>45.097040568478128</v>
+      </c>
+      <c r="R58">
+        <v>20.84663745360826</v>
+      </c>
+    </row>
+    <row r="59" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O59" t="s">
+        <v>127</v>
+      </c>
+      <c r="P59" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59">
+        <v>43.596440680795546</v>
+      </c>
+      <c r="R59">
+        <v>20.344290493195658</v>
+      </c>
+    </row>
+    <row r="60" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O60" t="s">
+        <v>128</v>
+      </c>
+      <c r="P60" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q60">
+        <v>45.028400841130193</v>
+      </c>
+      <c r="R60">
+        <v>18.536057756215531</v>
+      </c>
+    </row>
+    <row r="61" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O61" t="s">
+        <v>129</v>
+      </c>
+      <c r="P61" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q61">
+        <v>43.909501009694914</v>
+      </c>
+      <c r="R61">
+        <v>18.509077572060129</v>
+      </c>
+    </row>
+    <row r="62" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O62" t="s">
+        <v>130</v>
+      </c>
+      <c r="P62" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62">
+        <v>42.949587887664826</v>
+      </c>
+      <c r="R62">
+        <v>18.586912308288991</v>
+      </c>
+    </row>
+    <row r="63" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O63" t="s">
+        <v>131</v>
+      </c>
+      <c r="P63" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q63">
+        <v>41.447227797193548</v>
+      </c>
+      <c r="R63">
+        <v>18.94579969176068</v>
+      </c>
+    </row>
+    <row r="64" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O64" t="s">
+        <v>132</v>
+      </c>
+      <c r="P64" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q64">
+        <v>42.46848859554963</v>
+      </c>
+      <c r="R64">
+        <v>17.243662037032074</v>
+      </c>
+    </row>
+    <row r="65" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O65" t="s">
+        <v>133</v>
+      </c>
+      <c r="P65" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q65">
+        <v>42.168823403750778</v>
+      </c>
+      <c r="R65">
+        <v>22.051430620622011</v>
+      </c>
+    </row>
+    <row r="66" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O66" t="s">
+        <v>134</v>
+      </c>
+      <c r="P66" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q66">
+        <v>42.040561476929298</v>
+      </c>
+      <c r="R66">
+        <v>20.512939811451165</v>
+      </c>
+    </row>
+    <row r="67" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O67" t="s">
+        <v>135</v>
+      </c>
+      <c r="P67" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q67">
+        <v>44.016989300816427</v>
+      </c>
+      <c r="R67">
+        <v>24.001721623605508</v>
+      </c>
+    </row>
+    <row r="68" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O68" t="s">
+        <v>136</v>
+      </c>
+      <c r="P68" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q68">
+        <v>42.094041611128382</v>
+      </c>
+      <c r="R68">
+        <v>23.938884379520964</v>
+      </c>
+    </row>
+    <row r="69" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O69" t="s">
+        <v>137</v>
+      </c>
+      <c r="P69" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q69">
+        <v>48.783496529076743</v>
+      </c>
+      <c r="R69">
+        <v>18.762156855951417</v>
+      </c>
+    </row>
+    <row r="70" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O70" t="s">
+        <v>138</v>
+      </c>
+      <c r="P70" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q70">
+        <v>51.362579448452863</v>
+      </c>
+      <c r="R70">
+        <v>19.55962432092733</v>
+      </c>
+    </row>
+    <row r="71" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O71" t="s">
+        <v>139</v>
+      </c>
+      <c r="P71" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q71">
+        <v>55.091043640245957</v>
+      </c>
+      <c r="R71">
+        <v>22.239537799777505</v>
+      </c>
+    </row>
+    <row r="72" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O72" t="s">
+        <v>140</v>
+      </c>
+      <c r="P72" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72">
+        <v>54.431834100070169</v>
+      </c>
+      <c r="R72">
+        <v>20.308042768964359</v>
+      </c>
+    </row>
+    <row r="73" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O73" t="s">
+        <v>141</v>
+      </c>
+      <c r="P73" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q73">
+        <v>52.578068571541245</v>
+      </c>
+      <c r="R73">
+        <v>21.156306435359376</v>
+      </c>
+    </row>
+    <row r="74" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O74" t="s">
+        <v>142</v>
+      </c>
+      <c r="P74" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q74">
+        <v>52.492751329696326</v>
+      </c>
+      <c r="R74">
+        <v>22.601330578906001</v>
+      </c>
+    </row>
+    <row r="75" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O75" t="s">
+        <v>143</v>
+      </c>
+      <c r="P75" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q75">
+        <v>50.098329397050541</v>
+      </c>
+      <c r="R75">
+        <v>21.227689632791918</v>
+      </c>
+    </row>
+    <row r="76" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O76" t="s">
+        <v>144</v>
+      </c>
+      <c r="P76" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q76">
+        <v>49.10921344915964</v>
+      </c>
+      <c r="R76">
+        <v>22.333703694974677</v>
+      </c>
+    </row>
+    <row r="77" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O77" t="s">
+        <v>145</v>
+      </c>
+      <c r="P77" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q77">
+        <v>49.963581064223028</v>
+      </c>
+      <c r="R77">
+        <v>24.659147362711884</v>
+      </c>
+    </row>
+    <row r="78" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O78" t="s">
+        <v>146</v>
+      </c>
+      <c r="P78" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q78">
+        <v>51.027586802836062</v>
+      </c>
+      <c r="R78">
+        <v>23.438432924583903</v>
+      </c>
+    </row>
+    <row r="79" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O79" t="s">
+        <v>147</v>
+      </c>
+      <c r="P79" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q79">
+        <v>49.382271731160003</v>
+      </c>
+      <c r="R79">
+        <v>26.473535274665281</v>
+      </c>
+    </row>
+    <row r="80" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O80" t="s">
+        <v>148</v>
+      </c>
+      <c r="P80" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q80">
+        <v>48.443082890274951</v>
+      </c>
+      <c r="R80">
+        <v>25.631026260936768</v>
+      </c>
+    </row>
+    <row r="81" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O81" t="s">
+        <v>149</v>
+      </c>
+      <c r="P81" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81">
+        <v>46.090308886052881</v>
+      </c>
+      <c r="R81">
+        <v>24.928399561607801</v>
+      </c>
+    </row>
+    <row r="82" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O82" t="s">
+        <v>150</v>
+      </c>
+      <c r="P82" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q82">
+        <v>47.86701109128731</v>
+      </c>
+      <c r="R82">
+        <v>24.252269993260938</v>
+      </c>
+    </row>
+    <row r="83" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O83" t="s">
+        <v>151</v>
+      </c>
+      <c r="P83" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83">
+        <v>39.702713589727189</v>
+      </c>
+      <c r="R83">
+        <v>19.019127152983582</v>
+      </c>
+    </row>
+    <row r="84" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O84" t="s">
+        <v>152</v>
+      </c>
+      <c r="P84" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q84">
+        <v>41.016035398308624</v>
+      </c>
+      <c r="R84">
+        <v>16.711852980608981</v>
+      </c>
+    </row>
+    <row r="85" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O85" t="s">
+        <v>153</v>
+      </c>
+      <c r="P85" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q85">
+        <v>40.183591982076699</v>
+      </c>
+      <c r="R85">
+        <v>17.757012778750116</v>
+      </c>
+    </row>
+    <row r="86" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O86" t="s">
+        <v>154</v>
+      </c>
+      <c r="P86" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q86">
+        <v>50.679899069613121</v>
+      </c>
+      <c r="R86">
+        <v>25.081820363724571</v>
+      </c>
+    </row>
+    <row r="87" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O87" t="s">
+        <v>155</v>
+      </c>
+      <c r="P87" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q87">
+        <v>49.742975373040252</v>
+      </c>
+      <c r="R87">
+        <v>28.571824072953525</v>
+      </c>
+    </row>
+    <row r="88" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O88" t="s">
+        <v>156</v>
+      </c>
+      <c r="P88" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q88">
+        <v>50.420331270203192</v>
+      </c>
+      <c r="R88">
+        <v>27.691439479453503</v>
+      </c>
+    </row>
+    <row r="89" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O89" t="s">
+        <v>157</v>
+      </c>
+      <c r="P89" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89">
+        <v>39.190658405187023</v>
+      </c>
+      <c r="R89">
+        <v>19.994553566133973</v>
+      </c>
+    </row>
+    <row r="90" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O90" t="s">
+        <v>158</v>
+      </c>
+      <c r="P90" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q90">
+        <v>38.698960146751517</v>
+      </c>
+      <c r="R90">
+        <v>21.012349525270317</v>
+      </c>
+    </row>
+    <row r="91" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O91" t="s">
+        <v>159</v>
+      </c>
+      <c r="P91" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91">
+        <v>38.506436402600855</v>
+      </c>
+      <c r="R91">
+        <v>22.390931118905144</v>
+      </c>
+    </row>
+    <row r="92" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O92" t="s">
+        <v>160</v>
+      </c>
+      <c r="P92" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q92">
+        <v>37.742088180559023</v>
+      </c>
+      <c r="R92">
+        <v>23.832346097275707</v>
+      </c>
+    </row>
+    <row r="93" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O93" t="s">
+        <v>161</v>
+      </c>
+      <c r="P93" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q93">
+        <v>37.88253170553687</v>
+      </c>
+      <c r="R93">
+        <v>22.914679173342986</v>
+      </c>
+    </row>
+    <row r="94" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O94" t="s">
+        <v>162</v>
+      </c>
+      <c r="P94" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94">
+        <v>35.045033675996081</v>
+      </c>
+      <c r="R94">
+        <v>27.350248221293629</v>
+      </c>
+    </row>
+    <row r="95" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O95" t="s">
+        <v>163</v>
+      </c>
+      <c r="P95" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q95">
+        <v>36.833195571278637</v>
+      </c>
+      <c r="R95">
+        <v>24.286332540031161</v>
+      </c>
+    </row>
+    <row r="96" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O96" t="s">
+        <v>164</v>
+      </c>
+      <c r="P96" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96">
+        <v>36.876940507601439</v>
+      </c>
+      <c r="R96">
+        <v>25.351553609518287</v>
+      </c>
+    </row>
+    <row r="97" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O97" t="s">
+        <v>165</v>
+      </c>
+      <c r="P97" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q97">
+        <v>35.845406628777241</v>
+      </c>
+      <c r="R97">
+        <v>26.012926456286603</v>
+      </c>
+    </row>
+    <row r="98" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O98" t="s">
+        <v>166</v>
+      </c>
+      <c r="P98" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q98">
+        <v>48.811075278065445</v>
+      </c>
+      <c r="R98">
+        <v>27.205897030654054</v>
+      </c>
+    </row>
+    <row r="99" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O99" t="s">
+        <v>167</v>
+      </c>
+      <c r="P99" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q99">
+        <v>50.479872652084886</v>
+      </c>
+      <c r="R99">
+        <v>24.466291631131707</v>
+      </c>
+    </row>
+    <row r="100" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O100" t="s">
+        <v>168</v>
+      </c>
+      <c r="P100" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100">
+        <v>47.994421080812671</v>
+      </c>
+      <c r="R100">
+        <v>25.961355707586872</v>
+      </c>
+    </row>
+    <row r="101" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O101" t="s">
+        <v>169</v>
+      </c>
+      <c r="P101" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101">
+        <v>47.838684449152801</v>
+      </c>
+      <c r="R101">
+        <v>24.122988373010298</v>
+      </c>
+    </row>
+    <row r="102" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O102" t="s">
+        <v>170</v>
+      </c>
+      <c r="P102" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q102">
+        <v>47.133201469282682</v>
+      </c>
+      <c r="R102">
+        <v>28.357959038647223</v>
+      </c>
+    </row>
+    <row r="103" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O103" t="s">
+        <v>171</v>
+      </c>
+      <c r="P103" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q103">
+        <v>45.528562589324473</v>
+      </c>
+      <c r="R103">
+        <v>28.351811991185802</v>
+      </c>
+    </row>
+    <row r="104" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O104" t="s">
+        <v>172</v>
+      </c>
+      <c r="P104" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q104">
+        <v>46.567321043807752</v>
+      </c>
+      <c r="R104">
+        <v>26.391912861681234</v>
+      </c>
+    </row>
+    <row r="105" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O105" t="s">
+        <v>173</v>
+      </c>
+      <c r="P105" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q105">
+        <v>52.459013016362334</v>
+      </c>
+      <c r="R105">
+        <v>22.300027390675869</v>
+      </c>
+    </row>
+    <row r="106" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O106" t="s">
+        <v>174</v>
+      </c>
+      <c r="P106" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q106">
+        <v>52.560838577805882</v>
+      </c>
+      <c r="R106">
+        <v>20.508984052175109</v>
+      </c>
+    </row>
+    <row r="107" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O107" t="s">
+        <v>175</v>
+      </c>
+      <c r="P107" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q107">
+        <v>51.186038113812877</v>
+      </c>
+      <c r="R107">
+        <v>19.217817723931205</v>
+      </c>
+    </row>
+    <row r="108" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O108" t="s">
+        <v>176</v>
+      </c>
+      <c r="P108" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q108">
+        <v>54.370993396981127</v>
+      </c>
+      <c r="R108">
+        <v>20.210800640202265</v>
+      </c>
+    </row>
+    <row r="109" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O109" t="s">
+        <v>177</v>
+      </c>
+      <c r="P109" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q109">
+        <v>54.630478784113087</v>
+      </c>
+      <c r="R109">
+        <v>22.054707591532324</v>
+      </c>
+    </row>
+    <row r="110" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O110" t="s">
+        <v>178</v>
+      </c>
+      <c r="P110" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q110">
+        <v>47.805213456626056</v>
+      </c>
+      <c r="R110">
+        <v>18.106084200136131</v>
+      </c>
+    </row>
+    <row r="111" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O111" t="s">
+        <v>179</v>
+      </c>
+      <c r="P111" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q111">
+        <v>47.841088821852971</v>
+      </c>
+      <c r="R111">
+        <v>20.360360582892007</v>
+      </c>
+    </row>
+    <row r="112" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O112" t="s">
+        <v>180</v>
+      </c>
+      <c r="P112" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q112">
+        <v>49.692237574377721</v>
+      </c>
+      <c r="R112">
+        <v>20.300281698321417</v>
+      </c>
+    </row>
+    <row r="113" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O113" t="s">
+        <v>181</v>
+      </c>
+      <c r="P113" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q113">
+        <v>47.217679996306927</v>
+      </c>
+      <c r="R113">
+        <v>21.734165781562343</v>
+      </c>
+    </row>
+    <row r="114" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O114" t="s">
+        <v>182</v>
+      </c>
+      <c r="P114" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q114">
+        <v>50.009013874389126</v>
+      </c>
+      <c r="R114">
+        <v>22.157277237363445</v>
+      </c>
+    </row>
+    <row r="115" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O115" t="s">
+        <v>183</v>
+      </c>
+      <c r="P115" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q115">
+        <v>49.163968065389753</v>
+      </c>
+      <c r="R115">
+        <v>23.311417252962038</v>
+      </c>
+    </row>
+    <row r="116" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O116" t="s">
+        <v>184</v>
+      </c>
+      <c r="P116" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q116">
+        <v>43.028386970578332</v>
+      </c>
+      <c r="R116">
+        <v>18.504072990118871</v>
+      </c>
+    </row>
+    <row r="117" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O117" t="s">
+        <v>185</v>
+      </c>
+      <c r="P117" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q117">
+        <v>44.364405057169641</v>
+      </c>
+      <c r="R117">
+        <v>17.787561965790303</v>
+      </c>
+    </row>
+    <row r="118" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O118" t="s">
+        <v>186</v>
+      </c>
+      <c r="P118" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q118">
+        <v>41.756999515721283</v>
+      </c>
+      <c r="R118">
+        <v>21.290175202574641</v>
+      </c>
+    </row>
+    <row r="119" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O119" t="s">
+        <v>187</v>
+      </c>
+      <c r="P119" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q119">
+        <v>40.709378358070815</v>
+      </c>
+      <c r="R119">
+        <v>22.437678763514928</v>
+      </c>
+    </row>
+    <row r="120" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O120" t="s">
+        <v>188</v>
+      </c>
+      <c r="P120" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q120">
+        <v>39.285690938011783</v>
+      </c>
+      <c r="R120">
+        <v>25.05361565306109</v>
+      </c>
+    </row>
+    <row r="121" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O121" t="s">
+        <v>189</v>
+      </c>
+      <c r="P121" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q121">
+        <v>40.45265854886015</v>
+      </c>
+      <c r="R121">
+        <v>25.209590316691337</v>
+      </c>
+    </row>
+    <row r="122" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O122" t="s">
+        <v>190</v>
+      </c>
+      <c r="P122" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q122">
+        <v>39.508013293367519</v>
+      </c>
+      <c r="R122">
+        <v>23.515744612018075</v>
+      </c>
+    </row>
+    <row r="123" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O123" t="s">
+        <v>191</v>
+      </c>
+      <c r="P123" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q123">
+        <v>38.899862407825111</v>
+      </c>
+      <c r="R123">
+        <v>23.52563707180758</v>
+      </c>
+    </row>
+    <row r="124" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O124" t="s">
+        <v>192</v>
+      </c>
+      <c r="P124" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q124">
+        <v>38.993778539309119</v>
+      </c>
+      <c r="R124">
+        <v>21.934199090688679</v>
+      </c>
+    </row>
+    <row r="125" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O125" t="s">
+        <v>193</v>
+      </c>
+      <c r="P125" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q125">
+        <v>37.048449004982274</v>
+      </c>
+      <c r="R125">
+        <v>26.340106603426278</v>
+      </c>
+    </row>
+    <row r="126" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O126" t="s">
+        <v>194</v>
+      </c>
+      <c r="P126" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q126">
+        <v>38.234962921019445</v>
+      </c>
+      <c r="R126">
+        <v>25.471622855328288</v>
+      </c>
+    </row>
+    <row r="127" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O127" t="s">
+        <v>195</v>
+      </c>
+      <c r="P127" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q127">
+        <v>38.307451046097192</v>
+      </c>
+      <c r="R127">
+        <v>26.374329820482249</v>
+      </c>
+    </row>
+    <row r="128" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O128" t="s">
+        <v>196</v>
+      </c>
+      <c r="P128" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q128">
+        <v>41.789682822801048</v>
+      </c>
+      <c r="R128">
+        <v>18.05417062632829</v>
+      </c>
+    </row>
+    <row r="129" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O129" t="s">
+        <v>197</v>
+      </c>
+      <c r="P129" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q129">
+        <v>39.686515542046003</v>
+      </c>
+      <c r="R129">
+        <v>20.972158168711069</v>
+      </c>
+    </row>
+    <row r="130" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O130" t="s">
+        <v>198</v>
+      </c>
+      <c r="P130" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q130">
+        <v>35.005832998810973</v>
+      </c>
+      <c r="R130">
+        <v>28.667060709192938</v>
+      </c>
+    </row>
+    <row r="131" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O131" t="s">
+        <v>199</v>
+      </c>
+      <c r="P131" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q131">
+        <v>37.589150509918909</v>
+      </c>
+      <c r="R131">
+        <v>24.6321601818623</v>
+      </c>
+    </row>
+    <row r="132" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O132" t="s">
+        <v>200</v>
+      </c>
+      <c r="P132" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q132">
+        <v>45.186229426901264</v>
+      </c>
+      <c r="R132">
+        <v>24.618274730475115</v>
+      </c>
+    </row>
+    <row r="133" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O133" t="s">
+        <v>201</v>
+      </c>
+      <c r="P133" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q133">
+        <v>45.428841132289655</v>
+      </c>
+      <c r="R133">
+        <v>21.345540642098896</v>
+      </c>
+    </row>
+    <row r="134" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O134" t="s">
+        <v>202</v>
+      </c>
+      <c r="P134" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q134">
+        <v>46.306123049857767</v>
+      </c>
+      <c r="R134">
+        <v>23.125356721464534</v>
+      </c>
+    </row>
+    <row r="135" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O135" t="s">
+        <v>203</v>
+      </c>
+      <c r="P135" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q135">
+        <v>44.800578397945131</v>
+      </c>
+      <c r="R135">
+        <v>22.940690596532715</v>
+      </c>
+    </row>
+    <row r="136" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O136" t="s">
+        <v>204</v>
+      </c>
+      <c r="P136" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q136">
+        <v>46.339141804811867</v>
+      </c>
+      <c r="R136">
+        <v>18.81824737540364</v>
+      </c>
+    </row>
+    <row r="137" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O137" t="s">
+        <v>205</v>
+      </c>
+      <c r="P137" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q137">
+        <v>45.193612701421159</v>
+      </c>
+      <c r="R137">
+        <v>18.933599493970863</v>
+      </c>
+    </row>
+    <row r="138" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O138" t="s">
+        <v>206</v>
+      </c>
+      <c r="P138" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q138">
+        <v>42.646405324327418</v>
+      </c>
+      <c r="R138">
+        <v>22.941578442335341</v>
+      </c>
+    </row>
+    <row r="139" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O139" t="s">
+        <v>207</v>
+      </c>
+      <c r="P139" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q139">
+        <v>44.050658012344051</v>
+      </c>
+      <c r="R139">
+        <v>20.556469736380048</v>
+      </c>
+    </row>
+    <row r="140" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O140" t="s">
+        <v>208</v>
+      </c>
+      <c r="P140" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q140">
+        <v>43.416012448490548</v>
+      </c>
+      <c r="R140">
+        <v>19.598337378900105</v>
+      </c>
+    </row>
+    <row r="141" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O141" t="s">
+        <v>209</v>
+      </c>
+      <c r="P141" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q141">
+        <v>36.637800934120669</v>
+      </c>
+      <c r="R141">
+        <v>29.475300356909379</v>
+      </c>
+    </row>
+    <row r="142" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O142" t="s">
+        <v>210</v>
+      </c>
+      <c r="P142" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q142">
+        <v>36.273792554049933</v>
+      </c>
+      <c r="R142">
+        <v>27.98140547524558</v>
+      </c>
+    </row>
+    <row r="143" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O143" t="s">
+        <v>211</v>
+      </c>
+      <c r="P143" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q143">
+        <v>37.766317469537896</v>
+      </c>
+      <c r="R143">
+        <v>28.02179987783304</v>
+      </c>
+    </row>
+    <row r="144" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O144" t="s">
+        <v>212</v>
+      </c>
+      <c r="P144" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q144">
+        <v>38.055473097830003</v>
+      </c>
+      <c r="R144">
+        <v>31.236510837155564</v>
+      </c>
+    </row>
+    <row r="145" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O145" t="s">
+        <v>213</v>
+      </c>
+      <c r="P145" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q145">
+        <v>39.845927311574897</v>
+      </c>
+      <c r="R145">
+        <v>30.623492268763801</v>
+      </c>
+    </row>
+    <row r="146" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O146" t="s">
+        <v>214</v>
+      </c>
+      <c r="P146" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q146">
+        <v>39.72549414629281</v>
+      </c>
+      <c r="R146">
+        <v>27.236328734666611</v>
+      </c>
+    </row>
+    <row r="147" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O147" t="s">
+        <v>215</v>
+      </c>
+      <c r="P147" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q147">
+        <v>39.788467288556113</v>
+      </c>
+      <c r="R147">
+        <v>28.910100723545717</v>
+      </c>
+    </row>
+    <row r="148" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O148" t="s">
+        <v>216</v>
+      </c>
+      <c r="P148" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q148">
+        <v>41.589303505934801</v>
+      </c>
+      <c r="R148">
+        <v>30.557898767065812</v>
+      </c>
+    </row>
+    <row r="149" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O149" t="s">
+        <v>217</v>
+      </c>
+      <c r="P149" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q149">
+        <v>42.084676833097973</v>
+      </c>
+      <c r="R149">
+        <v>28.61790761232551</v>
+      </c>
+    </row>
+    <row r="150" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O150" t="s">
+        <v>218</v>
+      </c>
+      <c r="P150" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q150">
+        <v>43.914942608065815</v>
+      </c>
+      <c r="R150">
+        <v>29.147157266739796</v>
+      </c>
+    </row>
+    <row r="151" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O151" t="s">
+        <v>219</v>
+      </c>
+      <c r="P151" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q151">
+        <v>44.98956611414404</v>
+      </c>
+      <c r="R151">
+        <v>26.502781055463132</v>
+      </c>
+    </row>
+    <row r="152" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O152" t="s">
+        <v>220</v>
+      </c>
+      <c r="P152" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q152">
+        <v>43.518598178806094</v>
+      </c>
+      <c r="R152">
+        <v>27.187089236804209</v>
+      </c>
+    </row>
+    <row r="153" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O153" t="s">
+        <v>221</v>
+      </c>
+      <c r="P153" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q153">
+        <v>42.330522487626801</v>
+      </c>
+      <c r="R153">
+        <v>24.97837371454845</v>
+      </c>
+    </row>
+    <row r="154" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O154" t="s">
+        <v>222</v>
+      </c>
+      <c r="P154" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q154">
+        <v>41.83505397495388</v>
+      </c>
+      <c r="R154">
+        <v>26.699844062493472</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_SAU_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{357D3B03-21EF-4C64-910A-1EDB3DD5CF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52702281-EA5A-4288-BC69-6EE67F9EE76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2C01D35C-8632-4079-8D47-585E5002FA99}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CE247A5F-904F-4E11-9183-9B262D8F9AF3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9308648-2322-4D5E-A921-954EF84482A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CB31F16-5B89-411A-9720-B042249E0B0E}">
   <dimension ref="B3:R154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
